--- a/firmware/timings/4116-150.xlsx
+++ b/firmware/timings/4116-150.xlsx
@@ -287,7 +287,7 @@
     <t>Blank the State Machine's Output Shift Register.</t>
   </si>
   <si>
-    <t>tCPN</t>
+    <t>tCP[N]</t>
   </si>
   <si>
     <t>nop [4]</t>
@@ -728,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -830,6 +830,9 @@
     <xf borderId="3" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -851,7 +854,7 @@
     <xf borderId="9" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -5252,7 +5255,7 @@
       </c>
       <c r="K4" s="27">
         <f>J4+(OFFSET($B$4,$I4,0)+1)*cmd_time</f>
-        <v>123.3321</v>
+        <v>19.9998</v>
       </c>
       <c r="L4" s="25" t="s">
         <v>18</v>
@@ -5262,8 +5265,8 @@
       <c r="A5" s="28">
         <v>1.0</v>
       </c>
-      <c r="B5" s="23">
-        <v>31.0</v>
+      <c r="B5" s="29">
+        <v>0.0</v>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
@@ -5278,11 +5281,11 @@
       </c>
       <c r="J5" s="26">
         <f t="shared" ref="J5:J12" si="1">K4</f>
-        <v>123.3321</v>
+        <v>19.9998</v>
       </c>
       <c r="K5" s="27">
         <f>J5+(OFFSET($B$4,$I5,0)+1)*cmd_time</f>
-        <v>166.665</v>
+        <v>86.6658</v>
       </c>
       <c r="L5" s="25" t="s">
         <v>20</v>
@@ -5293,7 +5296,7 @@
         <v>2.0</v>
       </c>
       <c r="B6" s="29">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -5308,11 +5311,11 @@
       </c>
       <c r="J6" s="26">
         <f t="shared" si="1"/>
-        <v>166.665</v>
+        <v>86.6658</v>
       </c>
       <c r="K6" s="27">
         <f>J6+(OFFSET($B$4,$I6,0)+1)*cmd_time</f>
-        <v>169.9983</v>
+        <v>89.9991</v>
       </c>
       <c r="L6" s="25" t="s">
         <v>22</v>
@@ -5323,7 +5326,7 @@
         <v>3.0</v>
       </c>
       <c r="B7" s="29">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -5338,11 +5341,11 @@
       </c>
       <c r="J7" s="26">
         <f t="shared" si="1"/>
-        <v>169.9983</v>
+        <v>89.9991</v>
       </c>
       <c r="K7" s="27">
         <f>J7+(OFFSET($B$4,$I7,0)+1)*cmd_time</f>
-        <v>173.3316</v>
+        <v>93.3324</v>
       </c>
       <c r="L7" s="25" t="s">
         <v>24</v>
@@ -5353,7 +5356,7 @@
         <v>4.0</v>
       </c>
       <c r="B8" s="29">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
@@ -5368,11 +5371,11 @@
       </c>
       <c r="J8" s="26">
         <f t="shared" si="1"/>
-        <v>173.3316</v>
+        <v>93.3324</v>
       </c>
       <c r="K8" s="27">
         <f>J8+(OFFSET($B$4,$I8,0)+1)*cmd_time</f>
-        <v>186.6648</v>
+        <v>109.9989</v>
       </c>
       <c r="L8" s="25" t="s">
         <v>26</v>
@@ -5383,7 +5386,7 @@
         <v>5.0</v>
       </c>
       <c r="B9" s="29">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
@@ -5400,11 +5403,11 @@
       </c>
       <c r="J9" s="26">
         <f t="shared" si="1"/>
-        <v>186.6648</v>
+        <v>109.9989</v>
       </c>
       <c r="K9" s="27">
         <f>J9+(OFFSET($B$4,$I9,0)+1)*cmd_time</f>
-        <v>189.9981</v>
+        <v>113.3322</v>
       </c>
       <c r="L9" s="25" t="s">
         <v>29</v>
@@ -5414,8 +5417,8 @@
       <c r="A10" s="28">
         <v>6.0</v>
       </c>
-      <c r="B10" s="23">
-        <v>3.0</v>
+      <c r="B10" s="29">
+        <v>0.0</v>
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
@@ -5430,11 +5433,11 @@
       </c>
       <c r="J10" s="26">
         <f t="shared" si="1"/>
-        <v>189.9981</v>
+        <v>113.3322</v>
       </c>
       <c r="K10" s="27">
         <f>J10+(OFFSET($B$4,$I10,0)+1)*cmd_time</f>
-        <v>193.3314</v>
+        <v>116.6655</v>
       </c>
       <c r="L10" s="25" t="s">
         <v>31</v>
@@ -5445,7 +5448,7 @@
         <v>7.0</v>
       </c>
       <c r="B11" s="29">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
@@ -5460,11 +5463,11 @@
       </c>
       <c r="J11" s="30">
         <f t="shared" si="1"/>
-        <v>193.3314</v>
+        <v>116.6655</v>
       </c>
       <c r="K11" s="27">
         <f>J11+(OFFSET($B$4,$I11,0)+1)*cmd_time</f>
-        <v>196.6647</v>
+        <v>119.9988</v>
       </c>
       <c r="L11" s="25" t="s">
         <v>33</v>
@@ -5488,11 +5491,11 @@
       </c>
       <c r="J12" s="26">
         <f t="shared" si="1"/>
-        <v>196.6647</v>
+        <v>119.9988</v>
       </c>
       <c r="K12" s="27">
         <f>J12+(OFFSET($B$4,$I12,0)+1)*cmd_time</f>
-        <v>199.998</v>
+        <v>123.3321</v>
       </c>
       <c r="L12" s="25" t="s">
         <v>35</v>
@@ -5522,11 +5525,11 @@
       </c>
       <c r="J13" s="31">
         <f>K10</f>
-        <v>193.3314</v>
+        <v>116.6655</v>
       </c>
       <c r="K13" s="27">
         <f>J13+(OFFSET($B$4,$I13,0)+1)*cmd_time</f>
-        <v>196.6647</v>
+        <v>119.9988</v>
       </c>
       <c r="L13" s="25" t="s">
         <v>41</v>
@@ -5541,11 +5544,11 @@
       </c>
       <c r="C14" s="32">
         <f>B14 + (B14 * tolerance/100)</f>
-        <v>99.85</v>
+        <v>85</v>
       </c>
       <c r="D14" s="33">
         <f>ROUND(ras_low_start - ras_high_end,1)</f>
-        <v>166.7</v>
+        <v>86.7</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
@@ -5558,11 +5561,11 @@
       </c>
       <c r="J14" s="34">
         <f>K13</f>
-        <v>196.6647</v>
+        <v>119.9988</v>
       </c>
       <c r="K14" s="27">
         <f>J14+(OFFSET($B$4,$I14,0)+1)*cmd_time</f>
-        <v>199.998</v>
+        <v>123.3321</v>
       </c>
       <c r="L14" s="25" t="s">
         <v>44</v>
@@ -5573,15 +5576,15 @@
         <v>45</v>
       </c>
       <c r="B15" s="29">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C15" s="32">
         <f>B15 + (B15 * tolerance/100)</f>
-        <v>19.97</v>
+        <v>12.75</v>
       </c>
       <c r="D15" s="33">
         <f>ROUND(asc_start - ras_low_end, 1)</f>
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
@@ -5596,30 +5599,30 @@
       </c>
       <c r="J15" s="26">
         <f>K12</f>
-        <v>199.998</v>
+        <v>123.3321</v>
       </c>
       <c r="K15" s="27">
         <f>J15+(OFFSET($B$4,$I15,0)+1)*cmd_time</f>
-        <v>203.3313</v>
+        <v>126.6654</v>
       </c>
       <c r="L15" s="25" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="23">
-        <v>0.0</v>
+      <c r="B16" s="29">
+        <v>55.0</v>
       </c>
       <c r="C16" s="32">
         <f>B16 + (B16 * tolerance/100)</f>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="D16" s="33">
         <f>ROUND(max(cas_low_start_w-cas_high_end,cas_low_start_r-cas_high_end),1)</f>
-        <v>190</v>
+        <v>113.3</v>
       </c>
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
@@ -5632,11 +5635,11 @@
       </c>
       <c r="J16" s="26">
         <f t="shared" ref="J16:J24" si="2">K15</f>
-        <v>203.3313</v>
+        <v>126.6654</v>
       </c>
       <c r="K16" s="27">
         <f>J16+(OFFSET($B$4,$I16,0)+1)*cmd_time</f>
-        <v>239.9976</v>
+        <v>176.6649</v>
       </c>
       <c r="L16" s="25" t="s">
         <v>51</v>
@@ -5651,11 +5654,11 @@
       </c>
       <c r="C17" s="32">
         <f>B17 + (B17 * tolerance/100)</f>
-        <v>24.9625</v>
+        <v>21.25</v>
       </c>
       <c r="D17" s="33">
         <f>ROUND(cas_low_start_w - ras_low_end,1)</f>
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="19"/>
@@ -5668,11 +5671,11 @@
       </c>
       <c r="J17" s="26">
         <f t="shared" si="2"/>
-        <v>239.9976</v>
+        <v>176.6649</v>
       </c>
       <c r="K17" s="27">
         <f>J17+(OFFSET($B$4,$I17,0)+1)*cmd_time</f>
-        <v>243.3309</v>
+        <v>179.9982</v>
       </c>
       <c r="L17" s="25" t="s">
         <v>53</v>
@@ -5687,11 +5690,11 @@
       </c>
       <c r="C18" s="32">
         <f>B18 + (B18 * tolerance/100)</f>
-        <v>49.925</v>
+        <v>42.5</v>
       </c>
       <c r="D18" s="33">
         <f>ROUND(cas_low_start_w - ras_low_end,1)</f>
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="19"/>
@@ -5704,11 +5707,11 @@
       </c>
       <c r="J18" s="26">
         <f t="shared" si="2"/>
-        <v>243.3309</v>
+        <v>179.9982</v>
       </c>
       <c r="K18" s="27">
         <f>J18+(OFFSET($B$4,$I18,0)+1)*cmd_time</f>
-        <v>246.6642</v>
+        <v>183.3315</v>
       </c>
       <c r="L18" s="25" t="s">
         <v>55</v>
@@ -5718,16 +5721,16 @@
       <c r="A19" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="35">
-        <v>45.0</v>
+      <c r="B19" s="36">
+        <v>30.0</v>
       </c>
       <c r="C19" s="32">
         <f>B19 + (B19 * tolerance/100)</f>
-        <v>44.9325</v>
+        <v>25.5</v>
       </c>
       <c r="D19" s="33">
         <f>ROUND(w_high_start_2 - cas_low_end_w, 1)</f>
-        <v>43.3</v>
+        <v>56.7</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
@@ -5740,11 +5743,11 @@
       </c>
       <c r="J19" s="26">
         <f t="shared" si="2"/>
-        <v>246.6642</v>
+        <v>183.3315</v>
       </c>
       <c r="K19" s="27">
         <f>J19+(OFFSET($B$4,$I19,0)+1)*cmd_time</f>
-        <v>296.6637</v>
+        <v>223.3311</v>
       </c>
       <c r="L19" s="25" t="s">
         <v>58</v>
@@ -5755,15 +5758,15 @@
         <v>59</v>
       </c>
       <c r="B20" s="29">
-        <v>45.0</v>
+        <v>30.0</v>
       </c>
       <c r="C20" s="32">
         <f>B20 + (B20 * tolerance/100)</f>
-        <v>44.9325</v>
+        <v>25.5</v>
       </c>
       <c r="D20" s="33">
         <f>ROUND(w_high_start_2 - w_low_end, 1)</f>
-        <v>43.3</v>
+        <v>56.7</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
@@ -5776,11 +5779,11 @@
       </c>
       <c r="J20" s="26">
         <f t="shared" si="2"/>
-        <v>296.6637</v>
+        <v>223.3311</v>
       </c>
       <c r="K20" s="27">
         <f>J20+(OFFSET($B$4,$I20,0)+1)*cmd_time</f>
-        <v>299.997</v>
+        <v>226.6644</v>
       </c>
       <c r="L20" s="25" t="s">
         <v>61</v>
@@ -5795,11 +5798,11 @@
       </c>
       <c r="C21" s="32">
         <f>B21 + (B21 * tolerance/100)</f>
-        <v>94.8575</v>
+        <v>80.75</v>
       </c>
       <c r="D21" s="33">
         <f>ROUND(w_high_start_2 - ras_low_end, 1)</f>
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -5812,11 +5815,11 @@
       </c>
       <c r="J21" s="26">
         <f t="shared" si="2"/>
-        <v>299.997</v>
+        <v>226.6644</v>
       </c>
       <c r="K21" s="27">
         <f>J21+(OFFSET($B$4,$I21,0)+1)*cmd_time</f>
-        <v>303.3303</v>
+        <v>229.9977</v>
       </c>
       <c r="L21" s="25" t="s">
         <v>63</v>
@@ -5827,15 +5830,15 @@
         <v>64</v>
       </c>
       <c r="B22" s="29">
-        <v>45.0</v>
+        <v>20.0</v>
       </c>
       <c r="C22" s="32">
         <f>B22 + (B22 * tolerance/100)</f>
-        <v>44.9325</v>
+        <v>17</v>
       </c>
       <c r="D22" s="33">
         <f>ROUND(col_clear_start - cas_low_end_w, 1)</f>
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="19"/>
@@ -5848,11 +5851,11 @@
       </c>
       <c r="J22" s="26">
         <f t="shared" si="2"/>
-        <v>303.3303</v>
+        <v>229.9977</v>
       </c>
       <c r="K22" s="27">
         <f>J22+(OFFSET($B$4,$I22,0)+1)*cmd_time</f>
-        <v>306.6636</v>
+        <v>233.331</v>
       </c>
       <c r="L22" s="25"/>
     </row>
@@ -5865,11 +5868,11 @@
       </c>
       <c r="C23" s="32">
         <f>B23 + (B23 * tolerance/100)</f>
-        <v>94.8575</v>
-      </c>
-      <c r="D23" s="36">
+        <v>80.75</v>
+      </c>
+      <c r="D23" s="37">
         <f>round(d_clear_start - ras_low_end, 1)</f>
-        <v>70</v>
+        <v>86.7</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
@@ -5882,11 +5885,11 @@
       </c>
       <c r="J23" s="26">
         <f t="shared" si="2"/>
-        <v>306.6636</v>
+        <v>233.331</v>
       </c>
       <c r="K23" s="27">
         <f>J23+(OFFSET($B$4,$I23,0)+1)*cmd_time</f>
-        <v>319.9968</v>
+        <v>236.6643</v>
       </c>
       <c r="L23" s="25" t="s">
         <v>68</v>
@@ -5901,11 +5904,11 @@
       </c>
       <c r="C24" s="32">
         <f>B24 + (B24 * tolerance/100)</f>
-        <v>149.775</v>
+        <v>127.5</v>
       </c>
       <c r="D24" s="33">
         <f>ROUND(valid_data_start -ras_low_end, 1)</f>
-        <v>123.3</v>
+        <v>130</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
@@ -5918,13 +5921,13 @@
       </c>
       <c r="J24" s="26">
         <f t="shared" si="2"/>
-        <v>319.9968</v>
+        <v>236.6643</v>
       </c>
       <c r="K24" s="27">
         <f>J24+(OFFSET($B$4,$I24,0)+1)*cmd_time</f>
-        <v>323.3301</v>
-      </c>
-      <c r="L24" s="37" t="s">
+        <v>239.9976</v>
+      </c>
+      <c r="L24" s="38" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5933,15 +5936,15 @@
         <v>72</v>
       </c>
       <c r="B25" s="29">
-        <v>100.0</v>
+        <v>75.0</v>
       </c>
       <c r="C25" s="32">
         <f>B25 + (B25 * tolerance/100)</f>
-        <v>99.85</v>
+        <v>63.75</v>
       </c>
       <c r="D25" s="33">
         <f>ROUND(cas_high_start - cas_low_end_w, 1)</f>
-        <v>103.3</v>
+        <v>106.7</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -5952,10 +5955,10 @@
       <c r="I25" s="25">
         <v>0.0</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="39">
         <v>0.0</v>
       </c>
-      <c r="K25" s="39">
+      <c r="K25" s="40">
         <f>J25+cmd_time</f>
         <v>3.3333</v>
       </c>
@@ -5970,11 +5973,11 @@
       </c>
       <c r="C26" s="32">
         <f>B26 + (B26 * tolerance/100)</f>
-        <v>149.775</v>
+        <v>127.5</v>
       </c>
       <c r="D26" s="33">
         <f>ROUND(cas_high_start - ras_low_end,1)</f>
-        <v>126.7</v>
+        <v>133.3</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -6007,11 +6010,11 @@
       </c>
       <c r="C27" s="32">
         <f>B27 + (B27 * tolerance/100)</f>
-        <v>59.91</v>
+        <v>51</v>
       </c>
       <c r="D27" s="33">
         <f>round(cas_high_start - w_low_end, 1)</f>
-        <v>103.3</v>
+        <v>106.7</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
@@ -6043,11 +6046,11 @@
       </c>
       <c r="C28" s="32">
         <f>B28 + (B28 * tolerance/100)</f>
-        <v>149.775</v>
+        <v>127.5</v>
       </c>
       <c r="D28" s="33">
         <f>ROUND(ras_high_start - ras_low_end, 1)</f>
-        <v>150</v>
+        <v>146.7</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
@@ -6072,16 +6075,16 @@
       <c r="A29" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="23">
-        <v>320.0</v>
+      <c r="B29" s="29">
+        <v>260.0</v>
       </c>
       <c r="C29" s="32">
         <f>B29 + (B29 * tolerance/100)</f>
-        <v>319.52</v>
+        <v>221</v>
       </c>
       <c r="D29" s="33">
         <f>ras_high_start</f>
-        <v>323.3301</v>
+        <v>239.9976</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
@@ -6109,13 +6112,13 @@
       <c r="B30" s="29">
         <v>60.0</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="41">
         <f>B30 + (B30 * tolerance/100)</f>
-        <v>59.91</v>
-      </c>
-      <c r="D30" s="41">
+        <v>51</v>
+      </c>
+      <c r="D30" s="42">
         <f>round(ras_high_start - w_low_end, 1)</f>
-        <v>126.7</v>
+        <v>120</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
@@ -6140,11 +6143,11 @@
       <c r="A31" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="42">
-        <v>-0.15</v>
-      </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="44"/>
+      <c r="B31" s="43">
+        <v>-15.0</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="45"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="23"/>
@@ -6154,7 +6157,7 @@
       <c r="I31" s="25">
         <v>7.0</v>
       </c>
-      <c r="J31" s="45"/>
+      <c r="J31" s="46"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25" t="s">
         <v>89</v>
@@ -6162,7 +6165,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19"/>
-      <c r="B32" s="46"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="24"/>
@@ -6174,17 +6177,17 @@
       <c r="I32" s="25">
         <v>0.0</v>
       </c>
-      <c r="J32" s="45"/>
+      <c r="J32" s="46"/>
       <c r="K32" s="25"/>
       <c r="L32" s="25"/>
     </row>
     <row r="33">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
